--- a/leaudio/autopts_report/report_2025_01_04_17_18_38.xlsx
+++ b/leaudio/autopts_report/report_2025_01_04_17_18_38.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="2900">
   <si>
-    <t>AutoPTS Report: 2025-01-05 14:03</t>
+    <t>AutoPTS Report: 2025-01-05 14:15</t>
   </si>
   <si>
     <t>Test Case</t>

--- a/leaudio/autopts_report/report_2025_01_04_17_18_38.xlsx
+++ b/leaudio/autopts_report/report_2025_01_04_17_18_38.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="2900">
   <si>
-    <t>AutoPTS Report: 2025-01-05 14:15</t>
+    <t>AutoPTS Report: 2025-01-05 14:20</t>
   </si>
   <si>
     <t>Test Case</t>
